--- a/medical_application_forms/050_medical_app_development_beta_participation_consent_form--medical_application_forms.xlsx
+++ b/medical_application_forms/050_medical_app_development_beta_participation_consent_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,8 +1083,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'version_1'}</t>
+          <t>version_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Version 1'}</t>
+          <t>Version 1</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'version_2'}</t>
+          <t>version_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Version 2'}</t>
+          <t>Version 2</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'version_3'}</t>
+          <t>version_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Version 3'}</t>
+          <t>Version 3</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'version_4'}</t>
+          <t>version_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Version 4'}</t>
+          <t>Version 4</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'macOS'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'watch'}</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Watch'}</t>
+          <t>Watch</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'laptop/desktop'}</t>
+          <t>laptop/desktop</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Laptop/Desktop'}</t>
+          <t>Laptop/Desktop</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
